--- a/output/roomself_excel/712.xlsx
+++ b/output/roomself_excel/712.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>145898</v>
+        <v>103424</v>
       </c>
       <c r="D2" t="n">
-        <v>3108</v>
+        <v>2692</v>
       </c>
       <c r="E2" t="n">
-        <v>451</v>
+        <v>356</v>
       </c>
       <c r="F2" t="n">
-        <v>352</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>91204</v>
+        <v>109766</v>
       </c>
       <c r="D3" t="n">
-        <v>2416</v>
+        <v>2852</v>
       </c>
       <c r="E3" t="n">
-        <v>315</v>
+        <v>366</v>
       </c>
       <c r="F3" t="n">
-        <v>315</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36960</v>
+        <v>22041</v>
       </c>
       <c r="D4" t="n">
-        <v>2132</v>
+        <v>1320</v>
       </c>
       <c r="E4" t="n">
-        <v>409</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>155</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>137065</v>
+        <v>16856</v>
       </c>
       <c r="D5" t="n">
-        <v>2968</v>
+        <v>1080</v>
       </c>
       <c r="E5" t="n">
-        <v>347</v>
+        <v>185</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>60417</v>
+        <v>50163</v>
       </c>
       <c r="D6" t="n">
-        <v>2312</v>
+        <v>2120</v>
       </c>
       <c r="E6" t="n">
-        <v>457</v>
+        <v>159</v>
       </c>
       <c r="F6" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22041</v>
+        <v>92844</v>
       </c>
       <c r="D7" t="n">
-        <v>1320</v>
+        <v>4196</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>369</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>103424</v>
+        <v>60152</v>
       </c>
       <c r="D9" t="n">
-        <v>2692</v>
+        <v>1992</v>
       </c>
       <c r="E9" t="n">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="F9" t="n">
-        <v>311</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>715</v>
+        <v>51418</v>
       </c>
       <c r="D10" t="n">
-        <v>272</v>
+        <v>1884</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67234</v>
+        <v>23912</v>
       </c>
       <c r="D11" t="n">
-        <v>2956</v>
+        <v>1532</v>
       </c>
       <c r="E11" t="n">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="F11" t="n">
-        <v>294</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>109766</v>
+        <v>56004</v>
       </c>
       <c r="D12" t="n">
-        <v>2852</v>
+        <v>1944</v>
       </c>
       <c r="E12" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>92844</v>
+        <v>145898</v>
       </c>
       <c r="D13" t="n">
-        <v>4196</v>
+        <v>3108</v>
       </c>
       <c r="E13" t="n">
-        <v>496</v>
+        <v>451</v>
       </c>
       <c r="F13" t="n">
-        <v>369</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>231</v>
+        <v>91204</v>
       </c>
       <c r="D14" t="n">
-        <v>128</v>
+        <v>2416</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>84</v>
+        <v>36960</v>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>2132</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7076</v>
+        <v>137065</v>
       </c>
       <c r="D16" t="n">
-        <v>708</v>
+        <v>2968</v>
       </c>
       <c r="E16" t="n">
-        <v>132</v>
+        <v>347</v>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16856</v>
+        <v>60417</v>
       </c>
       <c r="D17" t="n">
-        <v>1080</v>
+        <v>2312</v>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>457</v>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>135867</v>
+        <v>715</v>
       </c>
       <c r="D18" t="n">
-        <v>3008</v>
+        <v>272</v>
       </c>
       <c r="E18" t="n">
-        <v>440</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
-        <v>342</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>60152</v>
+        <v>67234</v>
       </c>
       <c r="D19" t="n">
-        <v>1992</v>
+        <v>2956</v>
       </c>
       <c r="E19" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F19" t="n">
-        <v>221</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>51418</v>
+        <v>231</v>
       </c>
       <c r="D20" t="n">
-        <v>1884</v>
+        <v>128</v>
       </c>
       <c r="E20" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>43502</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>1920</v>
+        <v>76</v>
       </c>
       <c r="E21" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23912</v>
+        <v>7076</v>
       </c>
       <c r="D22" t="n">
-        <v>1532</v>
+        <v>708</v>
       </c>
       <c r="E22" t="n">
-        <v>499</v>
+        <v>132</v>
       </c>
       <c r="F22" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>56004</v>
+        <v>135867</v>
       </c>
       <c r="D23" t="n">
-        <v>1944</v>
+        <v>3008</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24">
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50163</v>
+        <v>43502</v>
       </c>
       <c r="D24" t="n">
-        <v>2120</v>
+        <v>1920</v>
       </c>
       <c r="E24" t="n">
-        <v>354</v>
+        <v>157</v>
       </c>
       <c r="F24" t="n">
-        <v>331</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -982,7 +982,7 @@
         <v>1960</v>
       </c>
       <c r="E25" t="n">
-        <v>493</v>
+        <v>336</v>
       </c>
       <c r="F25" t="n">
         <v>199</v>
@@ -1004,10 +1004,10 @@
         <v>1016</v>
       </c>
       <c r="E26" t="n">
-        <v>316</v>
+        <v>157</v>
       </c>
       <c r="F26" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/712.xlsx
+++ b/output/roomself_excel/712.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>2692</v>
       </c>
-      <c r="E2" t="n">
-        <v>356</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>298</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>285</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>2852</v>
       </c>
-      <c r="E3" t="n">
-        <v>366</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>303</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>350</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,15 @@
       <c r="D4" t="n">
         <v>1320</v>
       </c>
-      <c r="E4" t="n">
-        <v>42</v>
-      </c>
-      <c r="F4" t="n">
-        <v>14</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +617,38 @@
       <c r="D5" t="n">
         <v>1080</v>
       </c>
-      <c r="E5" t="n">
-        <v>185</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>124</v>
+        <v>344</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>82</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>16</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +666,31 @@
       <c r="D6" t="n">
         <v>2120</v>
       </c>
-      <c r="E6" t="n">
-        <v>159</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>157</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>144</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +707,38 @@
       <c r="D7" t="n">
         <v>4196</v>
       </c>
-      <c r="E7" t="n">
-        <v>369</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>312</v>
+        <v>286</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>23</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>196</v>
+      </c>
+      <c r="M7" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +756,23 @@
       <c r="D8" t="n">
         <v>1524</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>79</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>13</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +789,31 @@
       <c r="D9" t="n">
         <v>1992</v>
       </c>
-      <c r="E9" t="n">
-        <v>307</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>221</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>206</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +830,23 @@
       <c r="D10" t="n">
         <v>1884</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>179</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>15</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +863,23 @@
       <c r="D11" t="n">
         <v>1532</v>
       </c>
-      <c r="E11" t="n">
-        <v>286</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="G11" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +896,15 @@
       <c r="D12" t="n">
         <v>1944</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +921,31 @@
       <c r="D13" t="n">
         <v>3108</v>
       </c>
-      <c r="E13" t="n">
-        <v>451</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>352</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>438</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +962,31 @@
       <c r="D14" t="n">
         <v>2416</v>
       </c>
-      <c r="E14" t="n">
-        <v>315</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>315</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>302</v>
+      </c>
+      <c r="J14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1003,31 @@
       <c r="D15" t="n">
         <v>2132</v>
       </c>
-      <c r="E15" t="n">
-        <v>409</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>155</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G15" t="n">
+        <v>15</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>394</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1044,31 @@
       <c r="D16" t="n">
         <v>2968</v>
       </c>
-      <c r="E16" t="n">
-        <v>347</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
+        <v>172</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>175</v>
+      </c>
+      <c r="J16" t="n">
         <v>16</v>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1085,31 @@
       <c r="D17" t="n">
         <v>2312</v>
       </c>
-      <c r="E17" t="n">
-        <v>457</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>153</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>441</v>
+      </c>
+      <c r="J17" t="n">
+        <v>16</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1126,23 @@
       <c r="D18" t="n">
         <v>272</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>55</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>16</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,11 +1159,38 @@
       <c r="D19" t="n">
         <v>2956</v>
       </c>
-      <c r="E19" t="n">
-        <v>304</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>280</v>
+        <v>190</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>13</v>
+      </c>
+      <c r="J19" t="n">
+        <v>13</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>159</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -871,12 +1208,15 @@
       <c r="D20" t="n">
         <v>128</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1233,15 @@
       <c r="D21" t="n">
         <v>76</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1258,31 @@
       <c r="D22" t="n">
         <v>708</v>
       </c>
-      <c r="E22" t="n">
-        <v>132</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>77</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="G22" t="n">
+        <v>16</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>116</v>
+      </c>
+      <c r="J22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1299,31 @@
       <c r="D23" t="n">
         <v>3008</v>
       </c>
-      <c r="E23" t="n">
-        <v>440</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>342</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>425</v>
+      </c>
+      <c r="J23" t="n">
+        <v>15</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1340,23 @@
       <c r="D24" t="n">
         <v>1920</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>157</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>15</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1373,31 @@
       <c r="D25" t="n">
         <v>1960</v>
       </c>
-      <c r="E25" t="n">
-        <v>336</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>199</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>306</v>
+      </c>
+      <c r="J25" t="n">
+        <v>15</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1414,31 @@
       <c r="D26" t="n">
         <v>1016</v>
       </c>
-      <c r="E26" t="n">
-        <v>157</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>124</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G26" t="n">
+        <v>17</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>140</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
